--- a/inputdcspt_All.xlsx
+++ b/inputdcspt_All.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JLM\Dropbox (Personal)\UNIVERSIDADE\GESTÃO\Direção DCSPT\DSD\questionario2026\Dasshboard_DSD_DCSPT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E48350B7-3F40-4541-9104-34D7CECDC6DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87FABD89-AFC2-47C9-B16D-6FFE3E7883DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{1DBEFD56-9363-4F8B-ACC0-4EF6F1086AB3}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="304">
   <si>
     <t>ID</t>
   </si>
@@ -479,9 +479,6 @@
     <t>João Lourenço Marques</t>
   </si>
   <si>
-    <t>José Manuel Gaspar Martins</t>
-  </si>
-  <si>
     <t>Margarida Miguel Costeira e Pereira</t>
   </si>
   <si>
@@ -933,9 +930,6 @@
   </si>
   <si>
     <t>Gonçalo Rosete</t>
-  </si>
-  <si>
-    <t>João Miguel Canas Tavares</t>
   </si>
   <si>
     <t>jose Carlos Mota</t>
@@ -1364,14 +1358,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07EF0390-B0FA-4A65-BFBE-627208925094}">
-  <dimension ref="A1:AM119"/>
+  <dimension ref="A1:AK119"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="55.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="8" width="8.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1403,13 +1397,13 @@
         <v>137</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>138</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>139</v>
@@ -1418,7 +1412,7 @@
         <v>140</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Q1" s="2" t="s">
         <v>141</v>
@@ -1430,7 +1424,7 @@
         <v>143</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="U1" s="2" t="s">
         <v>144</v>
@@ -1439,66 +1433,60 @@
         <v>145</v>
       </c>
       <c r="W1" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="Y1" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="Z1" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="Y1" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AA1" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AB1" s="2" t="s">
         <v>300</v>
-      </c>
-      <c r="AB1" s="2" t="s">
-        <v>301</v>
       </c>
       <c r="AC1" s="2" t="s">
         <v>148</v>
       </c>
       <c r="AD1" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="AE1" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="AF1" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="AG1" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="AE1" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="AF1" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AH1" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AI1" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="AJ1" s="2" t="s">
         <v>303</v>
-      </c>
-      <c r="AI1" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="AJ1" s="2" t="s">
-        <v>152</v>
       </c>
       <c r="AK1" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="AL1" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="AM1" s="2" t="s">
-        <v>154</v>
-      </c>
     </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C2" t="s">
         <v>157</v>
-      </c>
-      <c r="C2" t="s">
-        <v>158</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -1561,60 +1549,54 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Z2">
         <v>1</v>
       </c>
       <c r="AA2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AB2">
         <v>1</v>
       </c>
       <c r="AC2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD2">
         <v>1</v>
       </c>
       <c r="AE2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AG2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AH2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AI2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AJ2">
         <v>1</v>
       </c>
       <c r="AK2">
-        <v>5</v>
-      </c>
-      <c r="AL2">
-        <v>1</v>
-      </c>
-      <c r="AM2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -1680,57 +1662,51 @@
         <v>1</v>
       </c>
       <c r="Z3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF3">
         <v>1</v>
       </c>
       <c r="AG3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AH3">
         <v>1</v>
       </c>
       <c r="AI3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AJ3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK3">
-        <v>3</v>
-      </c>
-      <c r="AL3">
-        <v>2</v>
-      </c>
-      <c r="AM3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
@@ -1793,37 +1769,37 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z4">
         <v>1</v>
       </c>
       <c r="AA4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB4">
         <v>1</v>
       </c>
       <c r="AC4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD4">
         <v>1</v>
       </c>
       <c r="AE4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AF4">
         <v>1</v>
       </c>
       <c r="AG4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AH4">
         <v>1</v>
       </c>
       <c r="AI4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ4">
         <v>1</v>
@@ -1831,22 +1807,16 @@
       <c r="AK4">
         <v>1</v>
       </c>
-      <c r="AL4">
-        <v>1</v>
-      </c>
-      <c r="AM4">
-        <v>1</v>
-      </c>
     </row>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
@@ -1903,10 +1873,10 @@
         <v>1</v>
       </c>
       <c r="W5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="X5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y5">
         <v>1</v>
@@ -1927,16 +1897,16 @@
         <v>1</v>
       </c>
       <c r="AE5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AG5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AI5">
         <v>1</v>
@@ -1947,28 +1917,22 @@
       <c r="AK5">
         <v>1</v>
       </c>
-      <c r="AL5">
-        <v>1</v>
-      </c>
-      <c r="AM5">
-        <v>1</v>
-      </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D6" t="s">
         <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
@@ -2019,16 +1983,16 @@
         <v>2</v>
       </c>
       <c r="W6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Z6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA6">
         <v>4</v>
@@ -2037,25 +2001,25 @@
         <v>3</v>
       </c>
       <c r="AC6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AD6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AG6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH6">
         <v>1</v>
       </c>
       <c r="AI6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AJ6">
         <v>1</v>
@@ -2063,22 +2027,16 @@
       <c r="AK6">
         <v>3</v>
       </c>
-      <c r="AL6">
-        <v>1</v>
-      </c>
-      <c r="AM6">
-        <v>3</v>
-      </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D7" t="s">
         <v>10</v>
@@ -2135,43 +2093,43 @@
         <v>1</v>
       </c>
       <c r="W7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="X7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AD7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE7">
         <v>1</v>
       </c>
       <c r="AF7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AG7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH7">
         <v>1</v>
       </c>
       <c r="AI7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ7">
         <v>1</v>
@@ -2179,22 +2137,16 @@
       <c r="AK7">
         <v>2</v>
       </c>
-      <c r="AL7">
-        <v>1</v>
-      </c>
-      <c r="AM7">
-        <v>2</v>
-      </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
@@ -2254,34 +2206,34 @@
         <v>1</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y8">
         <v>1</v>
       </c>
       <c r="Z8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AA8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB8">
         <v>1</v>
       </c>
       <c r="AC8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD8">
         <v>1</v>
       </c>
       <c r="AE8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF8">
         <v>1</v>
       </c>
       <c r="AG8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH8">
         <v>1</v>
@@ -2295,19 +2247,13 @@
       <c r="AK8">
         <v>1</v>
       </c>
-      <c r="AL8">
-        <v>1</v>
-      </c>
-      <c r="AM8">
-        <v>1</v>
-      </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I9" t="s">
         <v>28</v>
@@ -2355,22 +2301,22 @@
         <v>1</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y9">
         <v>1</v>
       </c>
       <c r="Z9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AA9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB9">
         <v>1</v>
       </c>
       <c r="AC9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD9">
         <v>1</v>
@@ -2396,31 +2342,25 @@
       <c r="AK9">
         <v>1</v>
       </c>
-      <c r="AL9">
-        <v>1</v>
-      </c>
-      <c r="AM9">
-        <v>1</v>
-      </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D10" t="s">
         <v>10</v>
       </c>
       <c r="E10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G10" t="s">
         <v>20</v>
@@ -2471,10 +2411,10 @@
         <v>1</v>
       </c>
       <c r="X10">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z10">
         <v>4</v>
@@ -2486,48 +2426,42 @@
         <v>4</v>
       </c>
       <c r="AC10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AD10">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF10">
         <v>1</v>
       </c>
       <c r="AG10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH10">
         <v>1</v>
       </c>
       <c r="AI10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AJ10">
         <v>1</v>
       </c>
       <c r="AK10">
-        <v>5</v>
-      </c>
-      <c r="AL10">
-        <v>1</v>
-      </c>
-      <c r="AM10">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D11" t="s">
         <v>10</v>
@@ -2628,22 +2562,16 @@
       <c r="AK11">
         <v>1</v>
       </c>
-      <c r="AL11">
-        <v>1</v>
-      </c>
-      <c r="AM11">
-        <v>1</v>
-      </c>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D12" t="s">
         <v>10</v>
@@ -2741,22 +2669,16 @@
       <c r="AK12">
         <v>1</v>
       </c>
-      <c r="AL12">
-        <v>1</v>
-      </c>
-      <c r="AM12">
-        <v>1</v>
-      </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D13" t="s">
         <v>10</v>
@@ -2857,22 +2779,16 @@
       <c r="AK13">
         <v>1</v>
       </c>
-      <c r="AL13">
-        <v>1</v>
-      </c>
-      <c r="AM13">
-        <v>1</v>
-      </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D14" t="s">
         <v>10</v>
@@ -2970,22 +2886,16 @@
       <c r="AK14">
         <v>1</v>
       </c>
-      <c r="AL14">
-        <v>1</v>
-      </c>
-      <c r="AM14">
-        <v>1</v>
-      </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D15" t="s">
         <v>10</v>
@@ -3048,16 +2958,16 @@
         <v>1</v>
       </c>
       <c r="Y15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Z15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AB15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC15">
         <v>1</v>
@@ -3066,13 +2976,13 @@
         <v>1</v>
       </c>
       <c r="AE15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AF15">
         <v>1</v>
       </c>
       <c r="AG15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AH15">
         <v>1</v>
@@ -3086,22 +2996,16 @@
       <c r="AK15">
         <v>1</v>
       </c>
-      <c r="AL15">
-        <v>1</v>
-      </c>
-      <c r="AM15">
-        <v>1</v>
-      </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>38</v>
       </c>
       <c r="B16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C16" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D16" t="s">
         <v>10</v>
@@ -3158,66 +3062,60 @@
         <v>1</v>
       </c>
       <c r="W16">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="X16">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA16">
         <v>3</v>
       </c>
       <c r="AB16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD16">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE16">
         <v>2</v>
       </c>
       <c r="AF16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AG16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH16">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AI16">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AJ16">
         <v>1</v>
       </c>
       <c r="AK16">
-        <v>5</v>
-      </c>
-      <c r="AL16">
-        <v>1</v>
-      </c>
-      <c r="AM16">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D17" t="s">
         <v>10</v>
@@ -3277,16 +3175,16 @@
         <v>1</v>
       </c>
       <c r="Z17">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB17">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AC17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD17">
         <v>1</v>
@@ -3312,28 +3210,22 @@
       <c r="AK17">
         <v>1</v>
       </c>
-      <c r="AL17">
-        <v>1</v>
-      </c>
-      <c r="AM17">
-        <v>1</v>
-      </c>
     </row>
-    <row r="18" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>40</v>
       </c>
       <c r="B18" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D18" t="s">
         <v>37</v>
       </c>
       <c r="E18" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F18" t="s">
         <v>24</v>
@@ -3390,31 +3282,31 @@
         <v>1</v>
       </c>
       <c r="Y18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA18">
         <v>3</v>
       </c>
       <c r="AB18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD18">
         <v>1</v>
       </c>
       <c r="AE18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF18">
         <v>1</v>
       </c>
       <c r="AG18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH18">
         <v>1</v>
@@ -3428,22 +3320,16 @@
       <c r="AK18">
         <v>1</v>
       </c>
-      <c r="AL18">
-        <v>1</v>
-      </c>
-      <c r="AM18">
-        <v>1</v>
-      </c>
     </row>
-    <row r="19" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>41</v>
       </c>
       <c r="B19" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D19" t="s">
         <v>10</v>
@@ -3509,57 +3395,51 @@
         <v>1</v>
       </c>
       <c r="Z19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA19">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AB19">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AC19">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AD19">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF19">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AG19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH19">
         <v>1</v>
       </c>
       <c r="AI19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ19">
         <v>1</v>
       </c>
       <c r="AK19">
-        <v>2</v>
-      </c>
-      <c r="AL19">
-        <v>1</v>
-      </c>
-      <c r="AM19">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>43</v>
       </c>
       <c r="B20" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C20" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D20" t="s">
         <v>10</v>
@@ -3625,57 +3505,51 @@
         <v>1</v>
       </c>
       <c r="Z20">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB20">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AC20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE20">
         <v>1</v>
       </c>
       <c r="AF20">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AG20">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AH20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI20">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AJ20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK20">
-        <v>2</v>
-      </c>
-      <c r="AL20">
-        <v>1</v>
-      </c>
-      <c r="AM20">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>44</v>
       </c>
       <c r="B21" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D21" t="s">
         <v>10</v>
@@ -3741,16 +3615,16 @@
         <v>1</v>
       </c>
       <c r="Z21">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB21">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AC21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD21">
         <v>2</v>
@@ -3759,45 +3633,39 @@
         <v>1</v>
       </c>
       <c r="AF21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AG21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH21">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK21">
         <v>2</v>
       </c>
-      <c r="AL21">
-        <v>1</v>
-      </c>
-      <c r="AM21">
-        <v>2</v>
-      </c>
     </row>
-    <row r="22" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>45</v>
       </c>
       <c r="B22" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C22" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D22" t="s">
         <v>10</v>
       </c>
       <c r="E22" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F22" t="s">
         <v>16</v>
@@ -3848,37 +3716,37 @@
         <v>1</v>
       </c>
       <c r="W22">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z22">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA22">
         <v>2</v>
       </c>
       <c r="AB22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AC22">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AD22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE22">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AF22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AG22">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AH22">
         <v>1</v>
@@ -3890,24 +3758,18 @@
         <v>1</v>
       </c>
       <c r="AK22">
-        <v>4</v>
-      </c>
-      <c r="AL22">
-        <v>1</v>
-      </c>
-      <c r="AM22">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>46</v>
       </c>
       <c r="B23" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D23" t="s">
         <v>37</v>
@@ -3985,16 +3847,16 @@
         <v>1</v>
       </c>
       <c r="AD23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH23">
         <v>1</v>
@@ -4008,22 +3870,16 @@
       <c r="AK23">
         <v>1</v>
       </c>
-      <c r="AL23">
-        <v>1</v>
-      </c>
-      <c r="AM23">
-        <v>1</v>
-      </c>
     </row>
-    <row r="24" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>47</v>
       </c>
       <c r="B24" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C24" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D24" t="s">
         <v>10</v>
@@ -4080,19 +3936,19 @@
         <v>1</v>
       </c>
       <c r="W24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z24">
         <v>1</v>
       </c>
       <c r="AA24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB24">
         <v>1</v>
@@ -4104,16 +3960,16 @@
         <v>1</v>
       </c>
       <c r="AE24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF24">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AG24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH24">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AI24">
         <v>1</v>
@@ -4124,28 +3980,22 @@
       <c r="AK24">
         <v>1</v>
       </c>
-      <c r="AL24">
-        <v>1</v>
-      </c>
-      <c r="AM24">
-        <v>1</v>
-      </c>
     </row>
-    <row r="25" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>48</v>
       </c>
       <c r="B25" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C25" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D25" t="s">
         <v>10</v>
       </c>
       <c r="E25" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F25" t="s">
         <v>24</v>
@@ -4205,16 +4055,16 @@
         <v>1</v>
       </c>
       <c r="Z25">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB25">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AC25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD25">
         <v>1</v>
@@ -4226,36 +4076,30 @@
         <v>1</v>
       </c>
       <c r="AG25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH25">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AI25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ25">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AK25">
         <v>1</v>
       </c>
-      <c r="AL25">
-        <v>1</v>
-      </c>
-      <c r="AM25">
-        <v>1</v>
-      </c>
     </row>
-    <row r="26" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>49</v>
       </c>
       <c r="B26" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C26" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D26" t="s">
         <v>10</v>
@@ -4321,57 +4165,51 @@
         <v>1</v>
       </c>
       <c r="Z26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD26">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE26">
         <v>1</v>
       </c>
       <c r="AF26">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AG26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK26">
-        <v>1</v>
-      </c>
-      <c r="AL26">
-        <v>1</v>
-      </c>
-      <c r="AM26">
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>51</v>
       </c>
       <c r="B27" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C27" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D27" t="s">
         <v>10</v>
@@ -4434,13 +4272,13 @@
         <v>1</v>
       </c>
       <c r="Y27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z27">
         <v>1</v>
       </c>
       <c r="AA27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB27">
         <v>1</v>
@@ -4452,13 +4290,13 @@
         <v>1</v>
       </c>
       <c r="AE27">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AF27">
         <v>1</v>
       </c>
       <c r="AG27">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AH27">
         <v>1</v>
@@ -4472,22 +4310,16 @@
       <c r="AK27">
         <v>1</v>
       </c>
-      <c r="AL27">
-        <v>1</v>
-      </c>
-      <c r="AM27">
-        <v>1</v>
-      </c>
     </row>
-    <row r="28" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>52</v>
       </c>
       <c r="B28" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C28" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D28" t="s">
         <v>10</v>
@@ -4553,57 +4385,51 @@
         <v>1</v>
       </c>
       <c r="Z28">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA28">
         <v>1</v>
       </c>
       <c r="AB28">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AC28">
         <v>1</v>
       </c>
       <c r="AD28">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF28">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AG28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH28">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AI28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AJ28">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AK28">
-        <v>1</v>
-      </c>
-      <c r="AL28">
-        <v>1</v>
-      </c>
-      <c r="AM28">
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>53</v>
       </c>
       <c r="B29" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C29" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D29" t="s">
         <v>10</v>
@@ -4660,34 +4486,34 @@
         <v>2</v>
       </c>
       <c r="W29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z29">
         <v>4</v>
       </c>
       <c r="AA29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB29">
         <v>4</v>
       </c>
       <c r="AC29">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AD29">
         <v>4</v>
       </c>
       <c r="AE29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AG29">
         <v>3</v>
@@ -4702,24 +4528,18 @@
         <v>1</v>
       </c>
       <c r="AK29">
-        <v>3</v>
-      </c>
-      <c r="AL29">
-        <v>1</v>
-      </c>
-      <c r="AM29">
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>54</v>
       </c>
       <c r="B30" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C30" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D30" t="s">
         <v>10</v>
@@ -4782,28 +4602,28 @@
         <v>1</v>
       </c>
       <c r="Y30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z30">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA30">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB30">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC30">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AD30">
         <v>4</v>
       </c>
       <c r="AE30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF30">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AG30">
         <v>3</v>
@@ -4818,24 +4638,18 @@
         <v>1</v>
       </c>
       <c r="AK30">
-        <v>3</v>
-      </c>
-      <c r="AL30">
-        <v>1</v>
-      </c>
-      <c r="AM30">
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>55</v>
       </c>
       <c r="B31" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C31" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D31" t="s">
         <v>10</v>
@@ -4898,60 +4712,54 @@
         <v>1</v>
       </c>
       <c r="Y31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE31">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AF31">
         <v>1</v>
       </c>
       <c r="AG31">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AH31">
         <v>1</v>
       </c>
       <c r="AI31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ31">
         <v>1</v>
       </c>
       <c r="AK31">
-        <v>1</v>
-      </c>
-      <c r="AL31">
-        <v>1</v>
-      </c>
-      <c r="AM31">
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>56</v>
       </c>
       <c r="B32" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C32" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D32" t="s">
         <v>37</v>
@@ -5008,66 +4816,60 @@
         <v>1</v>
       </c>
       <c r="W32">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="X32">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z32">
         <v>1</v>
       </c>
       <c r="AA32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AG32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH32">
         <v>1</v>
       </c>
       <c r="AI32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ32">
         <v>1</v>
       </c>
       <c r="AK32">
-        <v>3</v>
-      </c>
-      <c r="AL32">
-        <v>1</v>
-      </c>
-      <c r="AM32">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>57</v>
       </c>
       <c r="B33" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C33" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D33" t="s">
         <v>10</v>
@@ -5124,19 +4926,19 @@
         <v>1</v>
       </c>
       <c r="W33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z33">
         <v>1</v>
       </c>
       <c r="AA33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB33">
         <v>1</v>
@@ -5148,16 +4950,16 @@
         <v>1</v>
       </c>
       <c r="AE33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF33">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AG33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH33">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AI33">
         <v>1</v>
@@ -5168,22 +4970,16 @@
       <c r="AK33">
         <v>1</v>
       </c>
-      <c r="AL33">
-        <v>1</v>
-      </c>
-      <c r="AM33">
-        <v>1</v>
-      </c>
     </row>
-    <row r="34" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>58</v>
       </c>
       <c r="B34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C34" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D34" t="s">
         <v>37</v>
@@ -5240,22 +5036,22 @@
         <v>1</v>
       </c>
       <c r="W34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC34">
         <v>1</v>
@@ -5264,16 +5060,16 @@
         <v>1</v>
       </c>
       <c r="AE34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF34">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AG34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH34">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AI34">
         <v>1</v>
@@ -5284,22 +5080,16 @@
       <c r="AK34">
         <v>1</v>
       </c>
-      <c r="AL34">
-        <v>1</v>
-      </c>
-      <c r="AM34">
-        <v>1</v>
-      </c>
     </row>
-    <row r="35" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>59</v>
       </c>
       <c r="B35" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C35" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D35" t="s">
         <v>10</v>
@@ -5362,16 +5152,16 @@
         <v>1</v>
       </c>
       <c r="Y35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z35">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB35">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AC35">
         <v>1</v>
@@ -5380,42 +5170,36 @@
         <v>1</v>
       </c>
       <c r="AE35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF35">
         <v>1</v>
       </c>
       <c r="AG35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH35">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AI35">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ35">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AK35">
-        <v>3</v>
-      </c>
-      <c r="AL35">
-        <v>1</v>
-      </c>
-      <c r="AM35">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>60</v>
       </c>
       <c r="B36" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C36" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D36" t="s">
         <v>10</v>
@@ -5484,13 +5268,13 @@
         <v>1</v>
       </c>
       <c r="AA36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB36">
         <v>1</v>
       </c>
       <c r="AC36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD36">
         <v>1</v>
@@ -5505,33 +5289,27 @@
         <v>1</v>
       </c>
       <c r="AH36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AI36">
         <v>1</v>
       </c>
       <c r="AJ36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AK36">
         <v>1</v>
       </c>
-      <c r="AL36">
-        <v>1</v>
-      </c>
-      <c r="AM36">
-        <v>1</v>
-      </c>
     </row>
-    <row r="37" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>61</v>
       </c>
       <c r="B37" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C37" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D37" t="s">
         <v>10</v>
@@ -5597,57 +5375,51 @@
         <v>1</v>
       </c>
       <c r="Z37">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA37">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB37">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AC37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD37">
         <v>1</v>
       </c>
       <c r="AE37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF37">
         <v>1</v>
       </c>
       <c r="AG37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH37">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AI37">
         <v>1</v>
       </c>
       <c r="AJ37">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AK37">
         <v>1</v>
       </c>
-      <c r="AL37">
-        <v>1</v>
-      </c>
-      <c r="AM37">
-        <v>1</v>
-      </c>
     </row>
-    <row r="38" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>62</v>
       </c>
       <c r="B38" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C38" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D38" t="s">
         <v>10</v>
@@ -5707,7 +5479,7 @@
         <v>1</v>
       </c>
       <c r="X38">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y38">
         <v>1</v>
@@ -5716,13 +5488,13 @@
         <v>4</v>
       </c>
       <c r="AA38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB38">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AC38">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD38">
         <v>1</v>
@@ -5748,22 +5520,16 @@
       <c r="AK38">
         <v>1</v>
       </c>
-      <c r="AL38">
-        <v>1</v>
-      </c>
-      <c r="AM38">
-        <v>1</v>
-      </c>
     </row>
-    <row r="39" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>63</v>
       </c>
       <c r="B39" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C39" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D39" t="s">
         <v>10</v>
@@ -5826,13 +5592,13 @@
         <v>1</v>
       </c>
       <c r="Y39">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Z39">
         <v>1</v>
       </c>
       <c r="AA39">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AB39">
         <v>1</v>
@@ -5844,42 +5610,36 @@
         <v>1</v>
       </c>
       <c r="AE39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI39">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AJ39">
         <v>1</v>
       </c>
       <c r="AK39">
-        <v>5</v>
-      </c>
-      <c r="AL39">
-        <v>1</v>
-      </c>
-      <c r="AM39">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>64</v>
       </c>
       <c r="B40" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D40" t="s">
         <v>10</v>
@@ -5942,28 +5702,28 @@
         <v>1</v>
       </c>
       <c r="Y40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z40">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA40">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC40">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AD40">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE40">
         <v>2</v>
       </c>
       <c r="AF40">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AG40">
         <v>2</v>
@@ -5972,30 +5732,24 @@
         <v>1</v>
       </c>
       <c r="AI40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK40">
-        <v>3</v>
-      </c>
-      <c r="AL40">
-        <v>2</v>
-      </c>
-      <c r="AM40">
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>65</v>
       </c>
       <c r="B41" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C41" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D41" t="s">
         <v>10</v>
@@ -6061,57 +5815,51 @@
         <v>1</v>
       </c>
       <c r="Z41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA41">
         <v>1</v>
       </c>
       <c r="AB41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC41">
         <v>1</v>
       </c>
       <c r="AD41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE41">
         <v>1</v>
       </c>
       <c r="AF41">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AG41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH41">
         <v>1</v>
       </c>
       <c r="AI41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ41">
         <v>1</v>
       </c>
       <c r="AK41">
-        <v>1</v>
-      </c>
-      <c r="AL41">
-        <v>1</v>
-      </c>
-      <c r="AM41">
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>66</v>
       </c>
       <c r="B42" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C42" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D42" t="s">
         <v>10</v>
@@ -6174,13 +5922,13 @@
         <v>1</v>
       </c>
       <c r="Z42">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA42">
         <v>1</v>
       </c>
       <c r="AB42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC42">
         <v>1</v>
@@ -6198,42 +5946,36 @@
         <v>1</v>
       </c>
       <c r="AH42">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AI42">
         <v>1</v>
       </c>
       <c r="AJ42">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AK42">
-        <v>1</v>
-      </c>
-      <c r="AL42">
-        <v>2</v>
-      </c>
-      <c r="AM42">
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>67</v>
       </c>
       <c r="B43" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C43" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D43" t="s">
         <v>10</v>
       </c>
       <c r="E43" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F43" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G43" t="s">
         <v>13</v>
@@ -6281,66 +6023,60 @@
         <v>2</v>
       </c>
       <c r="W43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA43">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB43">
         <v>5</v>
       </c>
       <c r="AC43">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AD43">
         <v>5</v>
       </c>
       <c r="AE43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF43">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AG43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ43">
         <v>1</v>
       </c>
       <c r="AK43">
-        <v>3</v>
-      </c>
-      <c r="AL43">
-        <v>1</v>
-      </c>
-      <c r="AM43">
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>68</v>
       </c>
       <c r="B44" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C44" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D44" t="s">
         <v>10</v>
@@ -6397,28 +6133,28 @@
         <v>5</v>
       </c>
       <c r="W44">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X44">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z44">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB44">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC44">
         <v>3</v>
       </c>
       <c r="AD44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE44">
         <v>3</v>
@@ -6427,36 +6163,30 @@
         <v>3</v>
       </c>
       <c r="AG44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI44">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AJ44">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AK44">
-        <v>5</v>
-      </c>
-      <c r="AL44">
-        <v>5</v>
-      </c>
-      <c r="AM44">
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>69</v>
       </c>
       <c r="B45" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C45" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D45" t="s">
         <v>10</v>
@@ -6516,63 +6246,57 @@
         <v>1</v>
       </c>
       <c r="X45">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA45">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AB45">
         <v>5</v>
       </c>
       <c r="AC45">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AD45">
         <v>5</v>
       </c>
       <c r="AE45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF45">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AG45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH45">
         <v>1</v>
       </c>
       <c r="AI45">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AJ45">
         <v>1</v>
       </c>
       <c r="AK45">
-        <v>4</v>
-      </c>
-      <c r="AL45">
-        <v>1</v>
-      </c>
-      <c r="AM45">
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>70</v>
       </c>
       <c r="B46" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C46" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D46" t="s">
         <v>10</v>
@@ -6632,63 +6356,57 @@
         <v>1</v>
       </c>
       <c r="X46">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y46">
         <v>1</v>
       </c>
       <c r="Z46">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB46">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD46">
         <v>4</v>
       </c>
       <c r="AE46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG46">
         <v>2</v>
       </c>
       <c r="AH46">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI46">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AJ46">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AK46">
-        <v>4</v>
-      </c>
-      <c r="AL46">
-        <v>5</v>
-      </c>
-      <c r="AM46">
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>71</v>
       </c>
       <c r="B47" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C47" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D47" t="s">
         <v>10</v>
@@ -6748,16 +6466,16 @@
         <v>1</v>
       </c>
       <c r="X47">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z47">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AA47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB47">
         <v>1</v>
@@ -6769,13 +6487,13 @@
         <v>1</v>
       </c>
       <c r="AE47">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AF47">
         <v>1</v>
       </c>
       <c r="AG47">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AH47">
         <v>1</v>
@@ -6789,22 +6507,16 @@
       <c r="AK47">
         <v>1</v>
       </c>
-      <c r="AL47">
-        <v>1</v>
-      </c>
-      <c r="AM47">
-        <v>1</v>
-      </c>
     </row>
-    <row r="48" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>72</v>
       </c>
       <c r="B48" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C48" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D48" t="s">
         <v>10</v>
@@ -6870,16 +6582,16 @@
         <v>1</v>
       </c>
       <c r="Z48">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA48">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AB48">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AC48">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AD48">
         <v>1</v>
@@ -6894,33 +6606,27 @@
         <v>1</v>
       </c>
       <c r="AH48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI48">
         <v>1</v>
       </c>
       <c r="AJ48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK48">
         <v>1</v>
       </c>
-      <c r="AL48">
-        <v>1</v>
-      </c>
-      <c r="AM48">
-        <v>1</v>
-      </c>
     </row>
-    <row r="49" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>73</v>
       </c>
       <c r="B49" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C49" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D49" t="s">
         <v>10</v>
@@ -7004,13 +6710,13 @@
         <v>1</v>
       </c>
       <c r="AF49">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AG49">
         <v>1</v>
       </c>
       <c r="AH49">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AI49">
         <v>1</v>
@@ -7021,22 +6727,16 @@
       <c r="AK49">
         <v>1</v>
       </c>
-      <c r="AL49">
-        <v>1</v>
-      </c>
-      <c r="AM49">
-        <v>1</v>
-      </c>
     </row>
-    <row r="50" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>74</v>
       </c>
       <c r="B50" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C50" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D50" t="s">
         <v>10</v>
@@ -7102,57 +6802,51 @@
         <v>1</v>
       </c>
       <c r="Z50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA50">
         <v>1</v>
       </c>
       <c r="AB50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE50">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF50">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AG50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH50">
         <v>1</v>
       </c>
       <c r="AI50">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AJ50">
         <v>1</v>
       </c>
       <c r="AK50">
-        <v>5</v>
-      </c>
-      <c r="AL50">
-        <v>1</v>
-      </c>
-      <c r="AM50">
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>75</v>
       </c>
       <c r="B51" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C51" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D51" t="s">
         <v>10</v>
@@ -7218,25 +6912,25 @@
         <v>1</v>
       </c>
       <c r="Z51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA51">
         <v>1</v>
       </c>
       <c r="AB51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC51">
         <v>1</v>
       </c>
       <c r="AD51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE51">
         <v>1</v>
       </c>
       <c r="AF51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AG51">
         <v>1</v>
@@ -7253,22 +6947,16 @@
       <c r="AK51">
         <v>1</v>
       </c>
-      <c r="AL51">
-        <v>1</v>
-      </c>
-      <c r="AM51">
-        <v>1</v>
-      </c>
     </row>
-    <row r="52" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>76</v>
       </c>
       <c r="B52" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C52" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D52" t="s">
         <v>10</v>
@@ -7334,25 +7022,25 @@
         <v>1</v>
       </c>
       <c r="Z52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA52">
         <v>1</v>
       </c>
       <c r="AB52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC52">
         <v>1</v>
       </c>
       <c r="AD52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE52">
         <v>1</v>
       </c>
       <c r="AF52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AG52">
         <v>1</v>
@@ -7369,28 +7057,22 @@
       <c r="AK52">
         <v>1</v>
       </c>
-      <c r="AL52">
-        <v>1</v>
-      </c>
-      <c r="AM52">
-        <v>1</v>
-      </c>
     </row>
-    <row r="53" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>77</v>
       </c>
       <c r="B53" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C53" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D53" t="s">
         <v>10</v>
       </c>
       <c r="E53" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F53" t="s">
         <v>16</v>
@@ -7450,57 +7132,51 @@
         <v>1</v>
       </c>
       <c r="Z53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA53">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AB53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC53">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AD53">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE53">
         <v>1</v>
       </c>
       <c r="AF53">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AG53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH53">
         <v>1</v>
       </c>
       <c r="AI53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ53">
         <v>1</v>
       </c>
       <c r="AK53">
-        <v>1</v>
-      </c>
-      <c r="AL53">
-        <v>1</v>
-      </c>
-      <c r="AM53">
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>78</v>
       </c>
       <c r="B54" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C54" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D54" t="s">
         <v>10</v>
@@ -7563,13 +7239,13 @@
         <v>1</v>
       </c>
       <c r="Y54">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z54">
         <v>1</v>
       </c>
       <c r="AA54">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB54">
         <v>1</v>
@@ -7581,42 +7257,36 @@
         <v>1</v>
       </c>
       <c r="AE54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF54">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH54">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI54">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AJ54">
         <v>1</v>
       </c>
       <c r="AK54">
-        <v>5</v>
-      </c>
-      <c r="AL54">
-        <v>1</v>
-      </c>
-      <c r="AM54">
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>79</v>
       </c>
       <c r="B55" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C55" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D55" t="s">
         <v>10</v>
@@ -7688,13 +7358,13 @@
         <v>1</v>
       </c>
       <c r="AB55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC55">
         <v>1</v>
       </c>
       <c r="AD55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE55">
         <v>1</v>
@@ -7703,7 +7373,7 @@
         <v>1</v>
       </c>
       <c r="AG55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH55">
         <v>1</v>
@@ -7715,30 +7385,24 @@
         <v>1</v>
       </c>
       <c r="AK55">
-        <v>2</v>
-      </c>
-      <c r="AL55">
-        <v>1</v>
-      </c>
-      <c r="AM55">
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>80</v>
       </c>
       <c r="B56" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C56" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D56" t="s">
         <v>10</v>
       </c>
       <c r="F56" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G56" t="s">
         <v>17</v>
@@ -7798,13 +7462,13 @@
         <v>1</v>
       </c>
       <c r="AA56">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AB56">
         <v>1</v>
       </c>
       <c r="AC56">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AD56">
         <v>1</v>
@@ -7830,22 +7494,16 @@
       <c r="AK56">
         <v>1</v>
       </c>
-      <c r="AL56">
-        <v>1</v>
-      </c>
-      <c r="AM56">
-        <v>1</v>
-      </c>
     </row>
-    <row r="57" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>81</v>
       </c>
       <c r="B57" t="s">
+        <v>218</v>
+      </c>
+      <c r="C57" t="s">
         <v>219</v>
-      </c>
-      <c r="C57" t="s">
-        <v>220</v>
       </c>
       <c r="D57" t="s">
         <v>10</v>
@@ -7854,7 +7512,7 @@
         <v>32</v>
       </c>
       <c r="F57" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G57" t="s">
         <v>13</v>
@@ -7905,16 +7563,16 @@
         <v>1</v>
       </c>
       <c r="X57">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z57">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AA57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB57">
         <v>1</v>
@@ -7926,19 +7584,19 @@
         <v>1</v>
       </c>
       <c r="AE57">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AF57">
         <v>1</v>
       </c>
       <c r="AG57">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AH57">
         <v>1</v>
       </c>
       <c r="AI57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ57">
         <v>1</v>
@@ -7946,22 +7604,16 @@
       <c r="AK57">
         <v>1</v>
       </c>
-      <c r="AL57">
-        <v>1</v>
-      </c>
-      <c r="AM57">
-        <v>1</v>
-      </c>
     </row>
-    <row r="58" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>82</v>
       </c>
       <c r="B58" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C58" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D58" t="s">
         <v>37</v>
@@ -8027,13 +7679,13 @@
         <v>1</v>
       </c>
       <c r="Z58">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA58">
         <v>1</v>
       </c>
       <c r="AB58">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AC58">
         <v>1</v>
@@ -8051,33 +7703,27 @@
         <v>1</v>
       </c>
       <c r="AH58">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AI58">
         <v>1</v>
       </c>
       <c r="AJ58">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AK58">
         <v>1</v>
       </c>
-      <c r="AL58">
-        <v>1</v>
-      </c>
-      <c r="AM58">
-        <v>1</v>
-      </c>
     </row>
-    <row r="59" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>83</v>
       </c>
       <c r="B59" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C59" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D59" t="s">
         <v>10</v>
@@ -8140,13 +7786,13 @@
         <v>1</v>
       </c>
       <c r="Y59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z59">
         <v>1</v>
       </c>
       <c r="AA59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB59">
         <v>1</v>
@@ -8158,13 +7804,13 @@
         <v>1</v>
       </c>
       <c r="AE59">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AF59">
         <v>1</v>
       </c>
       <c r="AG59">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AH59">
         <v>1</v>
@@ -8178,28 +7824,22 @@
       <c r="AK59">
         <v>1</v>
       </c>
-      <c r="AL59">
-        <v>1</v>
-      </c>
-      <c r="AM59">
-        <v>1</v>
-      </c>
     </row>
-    <row r="60" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>84</v>
       </c>
       <c r="B60" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C60" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D60" t="s">
         <v>10</v>
       </c>
       <c r="E60" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F60" t="s">
         <v>24</v>
@@ -8262,25 +7902,25 @@
         <v>1</v>
       </c>
       <c r="AA60">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB60">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AC60">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD60">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE60">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AF60">
         <v>1</v>
       </c>
       <c r="AG60">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AH60">
         <v>1</v>
@@ -8292,24 +7932,18 @@
         <v>1</v>
       </c>
       <c r="AK60">
-        <v>3</v>
-      </c>
-      <c r="AL60">
-        <v>1</v>
-      </c>
-      <c r="AM60">
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>85</v>
       </c>
       <c r="B61" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C61" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D61" t="s">
         <v>37</v>
@@ -8375,57 +8009,51 @@
         <v>1</v>
       </c>
       <c r="Z61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA61">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AB61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC61">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AD61">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE61">
         <v>1</v>
       </c>
       <c r="AF61">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AG61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH61">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AI61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ61">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AK61">
-        <v>3</v>
-      </c>
-      <c r="AL61">
-        <v>1</v>
-      </c>
-      <c r="AM61">
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>86</v>
       </c>
       <c r="B62" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C62" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D62" t="s">
         <v>37</v>
@@ -8491,28 +8119,28 @@
         <v>1</v>
       </c>
       <c r="Z62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB62">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC62">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD62">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF62">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AG62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH62">
         <v>1</v>
@@ -8526,22 +8154,16 @@
       <c r="AK62">
         <v>3</v>
       </c>
-      <c r="AL62">
-        <v>1</v>
-      </c>
-      <c r="AM62">
-        <v>3</v>
-      </c>
     </row>
-    <row r="63" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>87</v>
       </c>
       <c r="B63" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C63" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D63" t="s">
         <v>10</v>
@@ -8613,28 +8235,28 @@
         <v>1</v>
       </c>
       <c r="AB63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC63">
         <v>1</v>
       </c>
       <c r="AD63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE63">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AF63">
         <v>1</v>
       </c>
       <c r="AG63">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AH63">
         <v>1</v>
       </c>
       <c r="AI63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ63">
         <v>1</v>
@@ -8642,22 +8264,16 @@
       <c r="AK63">
         <v>1</v>
       </c>
-      <c r="AL63">
-        <v>1</v>
-      </c>
-      <c r="AM63">
-        <v>1</v>
-      </c>
     </row>
-    <row r="64" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>88</v>
       </c>
       <c r="B64" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C64" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D64" t="s">
         <v>37</v>
@@ -8723,13 +8339,13 @@
         <v>1</v>
       </c>
       <c r="Z64">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA64">
         <v>1</v>
       </c>
       <c r="AB64">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AC64">
         <v>1</v>
@@ -8738,51 +8354,45 @@
         <v>1</v>
       </c>
       <c r="AE64">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF64">
         <v>1</v>
       </c>
       <c r="AG64">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH64">
         <v>1</v>
       </c>
       <c r="AI64">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AJ64">
         <v>1</v>
       </c>
       <c r="AK64">
-        <v>4</v>
-      </c>
-      <c r="AL64">
-        <v>1</v>
-      </c>
-      <c r="AM64">
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>89</v>
       </c>
       <c r="B65" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C65" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D65" t="s">
         <v>10</v>
       </c>
       <c r="E65" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F65" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G65" t="s">
         <v>20</v>
@@ -8836,60 +8446,54 @@
         <v>1</v>
       </c>
       <c r="Y65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z65">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA65">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AB65">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC65">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AD65">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE65">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF65">
         <v>1</v>
       </c>
       <c r="AG65">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI65">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AJ65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK65">
-        <v>4</v>
-      </c>
-      <c r="AL65">
-        <v>1</v>
-      </c>
-      <c r="AM65">
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>90</v>
       </c>
       <c r="B66" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C66" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D66" t="s">
         <v>10</v>
@@ -8952,19 +8556,19 @@
         <v>1</v>
       </c>
       <c r="Y66">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA66">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AB66">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD66">
         <v>1</v>
@@ -8979,42 +8583,36 @@
         <v>1</v>
       </c>
       <c r="AH66">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AI66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ66">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AK66">
-        <v>2</v>
-      </c>
-      <c r="AL66">
-        <v>1</v>
-      </c>
-      <c r="AM66">
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>91</v>
       </c>
       <c r="B67" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C67" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D67" t="s">
         <v>10</v>
       </c>
       <c r="E67" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F67" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G67" t="s">
         <v>20</v>
@@ -9068,31 +8666,31 @@
         <v>1</v>
       </c>
       <c r="Y67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z67">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA67">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AB67">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC67">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AD67">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE67">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF67">
         <v>1</v>
       </c>
       <c r="AG67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH67">
         <v>1</v>
@@ -9101,27 +8699,21 @@
         <v>1</v>
       </c>
       <c r="AJ67">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AK67">
         <v>1</v>
       </c>
-      <c r="AL67">
-        <v>3</v>
-      </c>
-      <c r="AM67">
-        <v>1</v>
-      </c>
     </row>
-    <row r="68" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>92</v>
       </c>
       <c r="B68" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C68" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D68" t="s">
         <v>37</v>
@@ -9181,60 +8773,54 @@
         <v>1</v>
       </c>
       <c r="Y68">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z68">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA68">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AB68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF68">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG68">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH68">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI68">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AJ68">
         <v>1</v>
       </c>
       <c r="AK68">
-        <v>5</v>
-      </c>
-      <c r="AL68">
-        <v>1</v>
-      </c>
-      <c r="AM68">
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>93</v>
       </c>
       <c r="B69" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C69" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D69" t="s">
         <v>10</v>
@@ -9332,22 +8918,16 @@
       <c r="AK69">
         <v>1</v>
       </c>
-      <c r="AL69">
-        <v>1</v>
-      </c>
-      <c r="AM69">
-        <v>1</v>
-      </c>
     </row>
-    <row r="70" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>94</v>
       </c>
       <c r="B70" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C70" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D70" t="s">
         <v>10</v>
@@ -9445,28 +9025,22 @@
       <c r="AK70">
         <v>1</v>
       </c>
-      <c r="AL70">
-        <v>1</v>
-      </c>
-      <c r="AM70">
-        <v>1</v>
-      </c>
     </row>
-    <row r="71" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>95</v>
       </c>
       <c r="B71" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C71" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D71" t="s">
         <v>10</v>
       </c>
       <c r="E71" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F71" t="s">
         <v>26</v>
@@ -9561,22 +9135,16 @@
       <c r="AK71">
         <v>1</v>
       </c>
-      <c r="AL71">
-        <v>1</v>
-      </c>
-      <c r="AM71">
-        <v>1</v>
-      </c>
     </row>
-    <row r="72" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>96</v>
       </c>
       <c r="B72" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C72" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D72" t="s">
         <v>10</v>
@@ -9633,25 +9201,25 @@
         <v>1</v>
       </c>
       <c r="W72">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="X72">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC72">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD72">
         <v>1</v>
@@ -9660,39 +9228,33 @@
         <v>1</v>
       </c>
       <c r="AF72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG72">
         <v>1</v>
       </c>
       <c r="AH72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI72">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ72">
         <v>1</v>
       </c>
       <c r="AK72">
-        <v>3</v>
-      </c>
-      <c r="AL72">
-        <v>1</v>
-      </c>
-      <c r="AM72">
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>97</v>
       </c>
       <c r="B73" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C73" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D73" t="s">
         <v>10</v>
@@ -9749,19 +9311,19 @@
         <v>1</v>
       </c>
       <c r="W73">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="X73">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z73">
         <v>1</v>
       </c>
       <c r="AA73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB73">
         <v>1</v>
@@ -9773,16 +9335,16 @@
         <v>1</v>
       </c>
       <c r="AE73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF73">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AG73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH73">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AI73">
         <v>1</v>
@@ -9793,22 +9355,16 @@
       <c r="AK73">
         <v>1</v>
       </c>
-      <c r="AL73">
-        <v>1</v>
-      </c>
-      <c r="AM73">
-        <v>1</v>
-      </c>
     </row>
-    <row r="74" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>98</v>
       </c>
       <c r="B74" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C74" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D74" t="s">
         <v>10</v>
@@ -9868,63 +9424,57 @@
         <v>1</v>
       </c>
       <c r="X74">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y74">
         <v>1</v>
       </c>
       <c r="Z74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA74">
         <v>1</v>
       </c>
       <c r="AB74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC74">
         <v>1</v>
       </c>
       <c r="AD74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE74">
         <v>1</v>
       </c>
       <c r="AF74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG74">
         <v>1</v>
       </c>
       <c r="AH74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI74">
         <v>1</v>
       </c>
       <c r="AJ74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK74">
         <v>1</v>
       </c>
-      <c r="AL74">
-        <v>1</v>
-      </c>
-      <c r="AM74">
-        <v>1</v>
-      </c>
     </row>
-    <row r="75" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>99</v>
       </c>
       <c r="B75" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C75" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D75" t="s">
         <v>10</v>
@@ -9933,7 +9483,7 @@
         <v>42</v>
       </c>
       <c r="F75" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G75" t="s">
         <v>13</v>
@@ -9990,28 +9540,28 @@
         <v>1</v>
       </c>
       <c r="Z75">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB75">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD75">
         <v>1</v>
       </c>
       <c r="AE75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF75">
         <v>1</v>
       </c>
       <c r="AG75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH75">
         <v>1</v>
@@ -10025,22 +9575,16 @@
       <c r="AK75">
         <v>1</v>
       </c>
-      <c r="AL75">
-        <v>1</v>
-      </c>
-      <c r="AM75">
-        <v>1</v>
-      </c>
     </row>
-    <row r="76" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>100</v>
       </c>
       <c r="B76" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C76" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D76" t="s">
         <v>10</v>
@@ -10103,19 +9647,19 @@
         <v>1</v>
       </c>
       <c r="Y76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z76">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB76">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AC76">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD76">
         <v>3</v>
@@ -10124,39 +9668,33 @@
         <v>2</v>
       </c>
       <c r="AF76">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AG76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH76">
         <v>1</v>
       </c>
       <c r="AI76">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AJ76">
         <v>1</v>
       </c>
       <c r="AK76">
-        <v>5</v>
-      </c>
-      <c r="AL76">
-        <v>1</v>
-      </c>
-      <c r="AM76">
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>101</v>
       </c>
       <c r="B77" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C77" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D77" t="s">
         <v>37</v>
@@ -10222,63 +9760,57 @@
         <v>1</v>
       </c>
       <c r="Z77">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA77">
         <v>1</v>
       </c>
       <c r="AB77">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC77">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AD77">
         <v>3</v>
       </c>
       <c r="AE77">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AF77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG77">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI77">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AJ77">
         <v>1</v>
       </c>
       <c r="AK77">
-        <v>5</v>
-      </c>
-      <c r="AL77">
-        <v>1</v>
-      </c>
-      <c r="AM77">
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>102</v>
       </c>
       <c r="B78" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C78" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D78" t="s">
         <v>10</v>
       </c>
       <c r="E78" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F78" t="s">
         <v>16</v>
@@ -10338,57 +9870,51 @@
         <v>1</v>
       </c>
       <c r="Z78">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA78">
         <v>1</v>
       </c>
       <c r="AB78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC78">
         <v>1</v>
       </c>
       <c r="AD78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE78">
         <v>1</v>
       </c>
       <c r="AF78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG78">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH78">
         <v>1</v>
       </c>
       <c r="AI78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ78">
         <v>1</v>
       </c>
       <c r="AK78">
-        <v>4</v>
-      </c>
-      <c r="AL78">
-        <v>1</v>
-      </c>
-      <c r="AM78">
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>103</v>
       </c>
       <c r="B79" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C79" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D79" t="s">
         <v>10</v>
@@ -10448,7 +9974,7 @@
         <v>1</v>
       </c>
       <c r="Z79">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA79">
         <v>1</v>
@@ -10457,48 +9983,42 @@
         <v>3</v>
       </c>
       <c r="AC79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD79">
         <v>3</v>
       </c>
       <c r="AE79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG79">
         <v>1</v>
       </c>
       <c r="AH79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI79">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AJ79">
         <v>1</v>
       </c>
       <c r="AK79">
-        <v>5</v>
-      </c>
-      <c r="AL79">
-        <v>1</v>
-      </c>
-      <c r="AM79">
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>104</v>
       </c>
       <c r="B80" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C80" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D80" t="s">
         <v>10</v>
@@ -10564,25 +10084,25 @@
         <v>1</v>
       </c>
       <c r="Z80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE80">
         <v>1</v>
       </c>
       <c r="AF80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG80">
         <v>1</v>
@@ -10599,22 +10119,16 @@
       <c r="AK80">
         <v>1</v>
       </c>
-      <c r="AL80">
-        <v>1</v>
-      </c>
-      <c r="AM80">
-        <v>1</v>
-      </c>
     </row>
-    <row r="81" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>105</v>
       </c>
       <c r="B81" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C81" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D81" t="s">
         <v>10</v>
@@ -10677,60 +10191,54 @@
         <v>1</v>
       </c>
       <c r="Y81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z81">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB81">
         <v>3</v>
       </c>
       <c r="AC81">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF81">
         <v>2</v>
       </c>
       <c r="AG81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI81">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AJ81">
         <v>1</v>
       </c>
       <c r="AK81">
-        <v>4</v>
-      </c>
-      <c r="AL81">
-        <v>1</v>
-      </c>
-      <c r="AM81">
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>106</v>
       </c>
       <c r="B82" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C82" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D82" t="s">
         <v>10</v>
@@ -10796,25 +10304,25 @@
         <v>1</v>
       </c>
       <c r="Z82">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA82">
         <v>1</v>
       </c>
       <c r="AB82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC82">
         <v>1</v>
       </c>
       <c r="AD82">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE82">
         <v>1</v>
       </c>
       <c r="AF82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG82">
         <v>1</v>
@@ -10831,22 +10339,16 @@
       <c r="AK82">
         <v>1</v>
       </c>
-      <c r="AL82">
-        <v>1</v>
-      </c>
-      <c r="AM82">
-        <v>1</v>
-      </c>
     </row>
-    <row r="83" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>107</v>
       </c>
       <c r="B83" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C83" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D83" t="s">
         <v>10</v>
@@ -10947,28 +10449,22 @@
       <c r="AK83">
         <v>1</v>
       </c>
-      <c r="AL83">
-        <v>1</v>
-      </c>
-      <c r="AM83">
-        <v>1</v>
-      </c>
     </row>
-    <row r="84" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>108</v>
       </c>
       <c r="B84" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C84" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D84" t="s">
         <v>10</v>
       </c>
       <c r="E84" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F84" t="s">
         <v>16</v>
@@ -11028,57 +10524,51 @@
         <v>1</v>
       </c>
       <c r="Z84">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA84">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB84">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC84">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD84">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE84">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF84">
         <v>1</v>
       </c>
       <c r="AG84">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH84">
         <v>1</v>
       </c>
       <c r="AI84">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AJ84">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AK84">
-        <v>5</v>
-      </c>
-      <c r="AL84">
-        <v>3</v>
-      </c>
-      <c r="AM84">
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>109</v>
       </c>
       <c r="B85" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C85" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D85" t="s">
         <v>10</v>
@@ -11135,66 +10625,60 @@
         <v>3</v>
       </c>
       <c r="W85">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="X85">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z85">
         <v>1</v>
       </c>
       <c r="AA85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB85">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AC85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD85">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE85">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF85">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AG85">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AH85">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AI85">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AJ85">
         <v>1</v>
       </c>
       <c r="AK85">
-        <v>5</v>
-      </c>
-      <c r="AL85">
-        <v>1</v>
-      </c>
-      <c r="AM85">
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>110</v>
       </c>
       <c r="B86" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C86" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D86" t="s">
         <v>10</v>
@@ -11254,31 +10738,31 @@
         <v>1</v>
       </c>
       <c r="X86">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z86">
         <v>4</v>
       </c>
       <c r="AA86">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB86">
         <v>4</v>
       </c>
       <c r="AC86">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AD86">
         <v>4</v>
       </c>
       <c r="AE86">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF86">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AG86">
         <v>3</v>
@@ -11293,24 +10777,18 @@
         <v>1</v>
       </c>
       <c r="AK86">
-        <v>3</v>
-      </c>
-      <c r="AL86">
-        <v>1</v>
-      </c>
-      <c r="AM86">
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>111</v>
       </c>
       <c r="B87" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C87" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D87" t="s">
         <v>37</v>
@@ -11373,60 +10851,54 @@
         <v>1</v>
       </c>
       <c r="Y87">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z87">
         <v>1</v>
       </c>
       <c r="AA87">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB87">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AC87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD87">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE87">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AF87">
         <v>1</v>
       </c>
       <c r="AG87">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AH87">
         <v>1</v>
       </c>
       <c r="AI87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ87">
         <v>1</v>
       </c>
       <c r="AK87">
-        <v>2</v>
-      </c>
-      <c r="AL87">
-        <v>1</v>
-      </c>
-      <c r="AM87">
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>112</v>
       </c>
       <c r="B88" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C88" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D88" t="s">
         <v>10</v>
@@ -11492,13 +10964,13 @@
         <v>1</v>
       </c>
       <c r="Z88">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AA88">
         <v>1</v>
       </c>
       <c r="AB88">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AC88">
         <v>1</v>
@@ -11527,22 +10999,16 @@
       <c r="AK88">
         <v>1</v>
       </c>
-      <c r="AL88">
-        <v>1</v>
-      </c>
-      <c r="AM88">
-        <v>1</v>
-      </c>
     </row>
-    <row r="89" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>113</v>
       </c>
       <c r="B89" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C89" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D89" t="s">
         <v>10</v>
@@ -11608,13 +11074,13 @@
         <v>1</v>
       </c>
       <c r="Z89">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA89">
         <v>1</v>
       </c>
       <c r="AB89">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC89">
         <v>1</v>
@@ -11623,13 +11089,13 @@
         <v>1</v>
       </c>
       <c r="AE89">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF89">
         <v>1</v>
       </c>
       <c r="AG89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH89">
         <v>1</v>
@@ -11643,22 +11109,16 @@
       <c r="AK89">
         <v>1</v>
       </c>
-      <c r="AL89">
-        <v>1</v>
-      </c>
-      <c r="AM89">
-        <v>1</v>
-      </c>
     </row>
-    <row r="90" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>114</v>
       </c>
       <c r="B90" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C90" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D90" t="s">
         <v>10</v>
@@ -11721,16 +11181,16 @@
         <v>1</v>
       </c>
       <c r="Y90">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Z90">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA90">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AB90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC90">
         <v>1</v>
@@ -11739,42 +11199,36 @@
         <v>1</v>
       </c>
       <c r="AE90">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF90">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AG90">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH90">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AI90">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AJ90">
         <v>1</v>
       </c>
       <c r="AK90">
-        <v>5</v>
-      </c>
-      <c r="AL90">
-        <v>1</v>
-      </c>
-      <c r="AM90">
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>115</v>
       </c>
       <c r="B91" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C91" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D91" t="s">
         <v>10</v>
@@ -11831,19 +11285,19 @@
         <v>1</v>
       </c>
       <c r="W91">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X91">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y91">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z91">
         <v>1</v>
       </c>
       <c r="AA91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB91">
         <v>1</v>
@@ -11855,16 +11309,16 @@
         <v>1</v>
       </c>
       <c r="AE91">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF91">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AG91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH91">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AI91">
         <v>1</v>
@@ -11875,22 +11329,16 @@
       <c r="AK91">
         <v>1</v>
       </c>
-      <c r="AL91">
-        <v>1</v>
-      </c>
-      <c r="AM91">
-        <v>1</v>
-      </c>
     </row>
-    <row r="92" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>116</v>
       </c>
       <c r="B92" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C92" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D92" t="s">
         <v>10</v>
@@ -11950,13 +11398,13 @@
         <v>1</v>
       </c>
       <c r="Y92">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z92">
         <v>1</v>
       </c>
       <c r="AA92">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB92">
         <v>1</v>
@@ -11968,42 +11416,36 @@
         <v>1</v>
       </c>
       <c r="AE92">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF92">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AG92">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH92">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AI92">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ92">
         <v>1</v>
       </c>
       <c r="AK92">
-        <v>3</v>
-      </c>
-      <c r="AL92">
-        <v>1</v>
-      </c>
-      <c r="AM92">
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>117</v>
       </c>
       <c r="B93" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C93" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D93" t="s">
         <v>10</v>
@@ -12084,16 +11526,16 @@
         <v>1</v>
       </c>
       <c r="AE93">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF93">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AG93">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH93">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AI93">
         <v>1</v>
@@ -12104,22 +11546,16 @@
       <c r="AK93">
         <v>1</v>
       </c>
-      <c r="AL93">
-        <v>1</v>
-      </c>
-      <c r="AM93">
-        <v>1</v>
-      </c>
     </row>
-    <row r="94" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>118</v>
       </c>
       <c r="B94" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C94" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D94" t="s">
         <v>37</v>
@@ -12182,13 +11618,13 @@
         <v>1</v>
       </c>
       <c r="Y94">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z94">
         <v>1</v>
       </c>
       <c r="AA94">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB94">
         <v>1</v>
@@ -12200,42 +11636,36 @@
         <v>1</v>
       </c>
       <c r="AE94">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AF94">
         <v>1</v>
       </c>
       <c r="AG94">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AH94">
         <v>1</v>
       </c>
       <c r="AI94">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ94">
         <v>1</v>
       </c>
       <c r="AK94">
-        <v>3</v>
-      </c>
-      <c r="AL94">
-        <v>1</v>
-      </c>
-      <c r="AM94">
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>119</v>
       </c>
       <c r="B95" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C95" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D95" t="s">
         <v>10</v>
@@ -12295,19 +11725,19 @@
         <v>1</v>
       </c>
       <c r="X95">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y95">
         <v>1</v>
       </c>
       <c r="Z95">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AA95">
         <v>1</v>
       </c>
       <c r="AB95">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AC95">
         <v>1</v>
@@ -12316,42 +11746,36 @@
         <v>1</v>
       </c>
       <c r="AE95">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF95">
         <v>1</v>
       </c>
       <c r="AG95">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH95">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AI95">
         <v>1</v>
       </c>
       <c r="AJ95">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AK95">
         <v>1</v>
       </c>
-      <c r="AL95">
-        <v>1</v>
-      </c>
-      <c r="AM95">
-        <v>1</v>
-      </c>
     </row>
-    <row r="96" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>120</v>
       </c>
       <c r="B96" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C96" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D96" t="s">
         <v>10</v>
@@ -12417,16 +11841,16 @@
         <v>1</v>
       </c>
       <c r="Z96">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA96">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AB96">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AC96">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AD96">
         <v>1</v>
@@ -12452,22 +11876,16 @@
       <c r="AK96">
         <v>1</v>
       </c>
-      <c r="AL96">
-        <v>1</v>
-      </c>
-      <c r="AM96">
-        <v>1</v>
-      </c>
     </row>
-    <row r="97" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>121</v>
       </c>
       <c r="B97" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C97" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D97" t="s">
         <v>37</v>
@@ -12530,31 +11948,31 @@
         <v>1</v>
       </c>
       <c r="Z97">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA97">
         <v>1</v>
       </c>
       <c r="AB97">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC97">
         <v>1</v>
       </c>
       <c r="AD97">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE97">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF97">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AG97">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH97">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AI97">
         <v>1</v>
@@ -12565,22 +11983,16 @@
       <c r="AK97">
         <v>1</v>
       </c>
-      <c r="AL97">
-        <v>1</v>
-      </c>
-      <c r="AM97">
-        <v>1</v>
-      </c>
     </row>
-    <row r="98" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>122</v>
       </c>
       <c r="B98" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C98" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D98" t="s">
         <v>10</v>
@@ -12646,13 +12058,13 @@
         <v>1</v>
       </c>
       <c r="Z98">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA98">
         <v>1</v>
       </c>
       <c r="AB98">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AC98">
         <v>1</v>
@@ -12667,36 +12079,30 @@
         <v>1</v>
       </c>
       <c r="AG98">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH98">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AI98">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ98">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AK98">
         <v>1</v>
       </c>
-      <c r="AL98">
-        <v>1</v>
-      </c>
-      <c r="AM98">
-        <v>1</v>
-      </c>
     </row>
-    <row r="99" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>123</v>
       </c>
       <c r="B99" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C99" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D99" t="s">
         <v>37</v>
@@ -12762,16 +12168,16 @@
         <v>1</v>
       </c>
       <c r="Z99">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA99">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AB99">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AC99">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AD99">
         <v>1</v>
@@ -12786,33 +12192,27 @@
         <v>1</v>
       </c>
       <c r="AH99">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AI99">
         <v>1</v>
       </c>
       <c r="AJ99">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AK99">
         <v>1</v>
       </c>
-      <c r="AL99">
-        <v>1</v>
-      </c>
-      <c r="AM99">
-        <v>1</v>
-      </c>
     </row>
-    <row r="100" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>124</v>
       </c>
       <c r="B100" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C100" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D100" t="s">
         <v>37</v>
@@ -12872,63 +12272,57 @@
         <v>1</v>
       </c>
       <c r="X100">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z100">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA100">
         <v>2</v>
       </c>
       <c r="AB100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD100">
         <v>1</v>
       </c>
       <c r="AE100">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF100">
         <v>1</v>
       </c>
       <c r="AG100">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH100">
         <v>1</v>
       </c>
       <c r="AI100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ100">
         <v>1</v>
       </c>
       <c r="AK100">
-        <v>2</v>
-      </c>
-      <c r="AL100">
-        <v>1</v>
-      </c>
-      <c r="AM100">
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>125</v>
       </c>
       <c r="B101" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C101" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D101" t="s">
         <v>37</v>
@@ -12994,13 +12388,13 @@
         <v>1</v>
       </c>
       <c r="Z101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA101">
         <v>1</v>
       </c>
       <c r="AB101">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC101">
         <v>1</v>
@@ -13009,16 +12403,16 @@
         <v>1</v>
       </c>
       <c r="AE101">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF101">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AG101">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH101">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AI101">
         <v>1</v>
@@ -13029,22 +12423,16 @@
       <c r="AK101">
         <v>1</v>
       </c>
-      <c r="AL101">
-        <v>1</v>
-      </c>
-      <c r="AM101">
-        <v>1</v>
-      </c>
     </row>
-    <row r="102" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>126</v>
       </c>
       <c r="B102" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C102" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D102" t="s">
         <v>10</v>
@@ -13104,19 +12492,19 @@
         <v>1</v>
       </c>
       <c r="X102">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y102">
         <v>1</v>
       </c>
       <c r="Z102">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AA102">
         <v>1</v>
       </c>
       <c r="AB102">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AC102">
         <v>1</v>
@@ -13134,33 +12522,27 @@
         <v>1</v>
       </c>
       <c r="AH102">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AI102">
         <v>1</v>
       </c>
       <c r="AJ102">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AK102">
         <v>1</v>
       </c>
-      <c r="AL102">
-        <v>1</v>
-      </c>
-      <c r="AM102">
-        <v>1</v>
-      </c>
     </row>
-    <row r="103" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>127</v>
       </c>
       <c r="B103" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C103" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D103" t="s">
         <v>10</v>
@@ -13220,63 +12602,57 @@
         <v>1</v>
       </c>
       <c r="X103">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y103">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z103">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA103">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB103">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC103">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AD103">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE103">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF103">
         <v>1</v>
       </c>
       <c r="AG103">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH103">
         <v>1</v>
       </c>
       <c r="AI103">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AJ103">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK103">
-        <v>4</v>
-      </c>
-      <c r="AL103">
-        <v>2</v>
-      </c>
-      <c r="AM103">
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>128</v>
       </c>
       <c r="B104" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C104" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D104" t="s">
         <v>10</v>
@@ -13339,60 +12715,54 @@
         <v>1</v>
       </c>
       <c r="Y104">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z104">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA104">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB104">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AC104">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AD104">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE104">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF104">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AG104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH104">
         <v>1</v>
       </c>
       <c r="AI104">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ104">
         <v>1</v>
       </c>
       <c r="AK104">
-        <v>3</v>
-      </c>
-      <c r="AL104">
-        <v>1</v>
-      </c>
-      <c r="AM104">
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>129</v>
       </c>
       <c r="B105" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C105" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D105" t="s">
         <v>10</v>
@@ -13455,31 +12825,31 @@
         <v>1</v>
       </c>
       <c r="Y105">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z105">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA105">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AB105">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AC105">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AD105">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE105">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF105">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AG105">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH105">
         <v>1</v>
@@ -13488,27 +12858,21 @@
         <v>3</v>
       </c>
       <c r="AJ105">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AK105">
-        <v>3</v>
-      </c>
-      <c r="AL105">
-        <v>5</v>
-      </c>
-      <c r="AM105">
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>130</v>
       </c>
       <c r="B106" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C106" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D106" t="s">
         <v>10</v>
@@ -13571,13 +12935,13 @@
         <v>1</v>
       </c>
       <c r="Z106">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA106">
         <v>1</v>
       </c>
       <c r="AB106">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC106">
         <v>1</v>
@@ -13606,28 +12970,22 @@
       <c r="AK106">
         <v>1</v>
       </c>
-      <c r="AL106">
-        <v>1</v>
-      </c>
-      <c r="AM106">
-        <v>1</v>
-      </c>
     </row>
-    <row r="107" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>131</v>
       </c>
       <c r="B107" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C107" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D107" t="s">
         <v>10</v>
       </c>
       <c r="E107" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F107" t="s">
         <v>16</v>
@@ -13687,16 +13045,16 @@
         <v>1</v>
       </c>
       <c r="Z107">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA107">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB107">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC107">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD107">
         <v>1</v>
@@ -13708,13 +13066,13 @@
         <v>1</v>
       </c>
       <c r="AG107">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AH107">
         <v>1</v>
       </c>
       <c r="AI107">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AJ107">
         <v>1</v>
@@ -13722,22 +13080,16 @@
       <c r="AK107">
         <v>1</v>
       </c>
-      <c r="AL107">
-        <v>1</v>
-      </c>
-      <c r="AM107">
-        <v>1</v>
-      </c>
     </row>
-    <row r="108" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>132</v>
       </c>
       <c r="B108" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C108" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D108" t="s">
         <v>37</v>
@@ -13797,7 +13149,7 @@
         <v>1</v>
       </c>
       <c r="X108">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y108">
         <v>1</v>
@@ -13806,13 +13158,13 @@
         <v>4</v>
       </c>
       <c r="AA108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AB108">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AC108">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD108">
         <v>1</v>
@@ -13838,22 +13190,16 @@
       <c r="AK108">
         <v>1</v>
       </c>
-      <c r="AL108">
-        <v>1</v>
-      </c>
-      <c r="AM108">
-        <v>1</v>
-      </c>
     </row>
-    <row r="109" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>133</v>
       </c>
       <c r="B109" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C109" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D109" t="s">
         <v>10</v>
@@ -13919,57 +13265,51 @@
         <v>1</v>
       </c>
       <c r="Z109">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA109">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AB109">
         <v>5</v>
       </c>
       <c r="AC109">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD109">
         <v>5</v>
       </c>
       <c r="AE109">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF109">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AG109">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH109">
         <v>1</v>
       </c>
       <c r="AI109">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AJ109">
         <v>1</v>
       </c>
       <c r="AK109">
-        <v>1</v>
-      </c>
-      <c r="AL109">
-        <v>1</v>
-      </c>
-      <c r="AM109">
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>134</v>
       </c>
       <c r="B110" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C110" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D110" t="s">
         <v>10</v>
@@ -14029,63 +13369,57 @@
         <v>1</v>
       </c>
       <c r="X110">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Y110">
         <v>1</v>
       </c>
       <c r="Z110">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AB110">
         <v>4</v>
       </c>
       <c r="AC110">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD110">
         <v>4</v>
       </c>
       <c r="AE110">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF110">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG110">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH110">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI110">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ110">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AK110">
-        <v>4</v>
-      </c>
-      <c r="AL110">
-        <v>5</v>
-      </c>
-      <c r="AM110">
         <v>5</v>
       </c>
     </row>
-    <row r="111" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>135</v>
       </c>
       <c r="B111" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C111" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D111" t="s">
         <v>10</v>
@@ -14151,25 +13485,25 @@
         <v>1</v>
       </c>
       <c r="Z111">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA111">
         <v>1</v>
       </c>
       <c r="AB111">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC111">
         <v>1</v>
       </c>
       <c r="AD111">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE111">
         <v>1</v>
       </c>
       <c r="AF111">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AG111">
         <v>1</v>
@@ -14184,24 +13518,18 @@
         <v>1</v>
       </c>
       <c r="AK111">
-        <v>1</v>
-      </c>
-      <c r="AL111">
-        <v>1</v>
-      </c>
-      <c r="AM111">
         <v>5</v>
       </c>
     </row>
-    <row r="112" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>136</v>
       </c>
       <c r="B112" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C112" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D112" t="s">
         <v>10</v>
@@ -14210,7 +13538,7 @@
         <v>32</v>
       </c>
       <c r="F112" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G112" t="s">
         <v>13</v>
@@ -14282,13 +13610,13 @@
         <v>1</v>
       </c>
       <c r="AE112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF112">
         <v>1</v>
       </c>
       <c r="AG112">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH112">
         <v>1</v>
@@ -14302,22 +13630,16 @@
       <c r="AK112">
         <v>1</v>
       </c>
-      <c r="AL112">
-        <v>1</v>
-      </c>
-      <c r="AM112">
-        <v>1</v>
-      </c>
     </row>
-    <row r="113" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B113" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C113" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D113" t="s">
         <v>10</v>
@@ -14332,7 +13654,7 @@
         <v>20</v>
       </c>
       <c r="I113" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J113">
         <v>1</v>
@@ -14377,16 +13699,16 @@
         <v>1</v>
       </c>
       <c r="X113">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z113">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AA113">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB113">
         <v>1</v>
@@ -14398,16 +13720,16 @@
         <v>1</v>
       </c>
       <c r="AE113">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AF113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG113">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AH113">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI113">
         <v>1</v>
@@ -14418,22 +13740,16 @@
       <c r="AK113">
         <v>1</v>
       </c>
-      <c r="AL113">
-        <v>1</v>
-      </c>
-      <c r="AM113">
-        <v>1</v>
-      </c>
     </row>
-    <row r="114" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
+        <v>281</v>
+      </c>
+      <c r="B114" t="s">
         <v>282</v>
       </c>
-      <c r="B114" t="s">
-        <v>283</v>
-      </c>
       <c r="C114" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D114" t="s">
         <v>10</v>
@@ -14448,7 +13764,7 @@
         <v>20</v>
       </c>
       <c r="I114" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="J114">
         <v>1</v>
@@ -14511,16 +13827,16 @@
         <v>1</v>
       </c>
       <c r="AD114">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF114">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AG114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH114">
         <v>1</v>
@@ -14532,24 +13848,18 @@
         <v>1</v>
       </c>
       <c r="AK114">
-        <v>1</v>
-      </c>
-      <c r="AL114">
-        <v>1</v>
-      </c>
-      <c r="AM114">
         <v>3</v>
       </c>
     </row>
-    <row r="115" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
+        <v>283</v>
+      </c>
+      <c r="B115" t="s">
         <v>284</v>
       </c>
-      <c r="B115" t="s">
-        <v>285</v>
-      </c>
       <c r="C115" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D115" t="s">
         <v>10</v>
@@ -14564,7 +13874,7 @@
         <v>20</v>
       </c>
       <c r="I115" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="J115">
         <v>1</v>
@@ -14615,57 +13925,51 @@
         <v>1</v>
       </c>
       <c r="Z115">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA115">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AB115">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AC115">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AD115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE115">
         <v>1</v>
       </c>
       <c r="AF115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG115">
         <v>1</v>
       </c>
       <c r="AH115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI115">
         <v>1</v>
       </c>
       <c r="AJ115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK115">
         <v>1</v>
       </c>
-      <c r="AL115">
-        <v>1</v>
-      </c>
-      <c r="AM115">
-        <v>1</v>
-      </c>
     </row>
-    <row r="116" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
+        <v>285</v>
+      </c>
+      <c r="B116" t="s">
         <v>286</v>
       </c>
-      <c r="B116" t="s">
-        <v>287</v>
-      </c>
       <c r="C116" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D116" t="s">
         <v>10</v>
@@ -14680,7 +13984,7 @@
         <v>20</v>
       </c>
       <c r="I116" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J116">
         <v>1</v>
@@ -14746,42 +14050,36 @@
         <v>1</v>
       </c>
       <c r="AE116">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF116">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AG116">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH116">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AI116">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AJ116">
         <v>1</v>
       </c>
       <c r="AK116">
-        <v>4</v>
-      </c>
-      <c r="AL116">
-        <v>1</v>
-      </c>
-      <c r="AM116">
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
+        <v>287</v>
+      </c>
+      <c r="B117" t="s">
         <v>288</v>
       </c>
-      <c r="B117" t="s">
-        <v>289</v>
-      </c>
       <c r="C117" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D117" t="s">
         <v>10</v>
@@ -14796,7 +14094,7 @@
         <v>13</v>
       </c>
       <c r="I117" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J117">
         <v>1</v>
@@ -14844,60 +14142,54 @@
         <v>1</v>
       </c>
       <c r="Y117">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z117">
         <v>1</v>
       </c>
       <c r="AA117">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB117">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AC117">
         <v>1</v>
       </c>
       <c r="AD117">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE117">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AF117">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG117">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AH117">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI117">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ117">
         <v>1</v>
       </c>
       <c r="AK117">
-        <v>3</v>
-      </c>
-      <c r="AL117">
-        <v>1</v>
-      </c>
-      <c r="AM117">
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
+        <v>289</v>
+      </c>
+      <c r="B118" t="s">
         <v>290</v>
       </c>
-      <c r="B118" t="s">
-        <v>291</v>
-      </c>
       <c r="C118" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D118" t="s">
         <v>10</v>
@@ -14912,7 +14204,7 @@
         <v>13</v>
       </c>
       <c r="I118" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J118">
         <v>1</v>
@@ -14960,13 +14252,13 @@
         <v>1</v>
       </c>
       <c r="Y118">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z118">
         <v>1</v>
       </c>
       <c r="AA118">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB118">
         <v>1</v>
@@ -14978,42 +14270,36 @@
         <v>1</v>
       </c>
       <c r="AE118">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF118">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG118">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH118">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI118">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AJ118">
         <v>1</v>
       </c>
       <c r="AK118">
-        <v>5</v>
-      </c>
-      <c r="AL118">
-        <v>1</v>
-      </c>
-      <c r="AM118">
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
+        <v>291</v>
+      </c>
+      <c r="B119" t="s">
         <v>292</v>
       </c>
-      <c r="B119" t="s">
-        <v>293</v>
-      </c>
       <c r="C119" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D119" t="s">
         <v>10</v>
@@ -15022,7 +14308,7 @@
         <v>13</v>
       </c>
       <c r="I119" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J119">
         <v>1</v>
@@ -15070,13 +14356,13 @@
         <v>1</v>
       </c>
       <c r="Y119">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z119">
         <v>1</v>
       </c>
       <c r="AA119">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB119">
         <v>1</v>
@@ -15100,18 +14386,12 @@
         <v>1</v>
       </c>
       <c r="AI119">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ119">
         <v>1</v>
       </c>
       <c r="AK119">
-        <v>3</v>
-      </c>
-      <c r="AL119">
-        <v>1</v>
-      </c>
-      <c r="AM119">
         <v>1</v>
       </c>
     </row>
